--- a/data/Data_Desa_Longsor.xlsx
+++ b/data/Data_Desa_Longsor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Downloads\magangma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE2619C-B6ED-4529-AA9A-68C82FDB1DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB126A2D-923D-4BD8-999A-FD661C1D1537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7459FBA0-8F84-40E5-A481-1D7B463EEB8F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="170">
   <si>
     <t>ancaman</t>
   </si>
@@ -58,19 +58,519 @@
   </si>
   <si>
     <t>teredukasi</t>
+  </si>
+  <si>
+    <t>TANAH LONGSOR</t>
+  </si>
+  <si>
+    <t>Batujajar</t>
+  </si>
+  <si>
+    <t>Desa Batujajar Barat</t>
+  </si>
+  <si>
+    <t>Desa Batujajar Timur</t>
+  </si>
+  <si>
+    <t>Desa Giriasih</t>
+  </si>
+  <si>
+    <t>Desa Selacau</t>
+  </si>
+  <si>
+    <t>Cihampelas</t>
+  </si>
+  <si>
+    <t>Desa Cipatik</t>
+  </si>
+  <si>
+    <t>Desa Citapen</t>
+  </si>
+  <si>
+    <t>Desa Pataruman</t>
+  </si>
+  <si>
+    <t>Desa Singajaya</t>
+  </si>
+  <si>
+    <t>Desa Situwangi</t>
+  </si>
+  <si>
+    <t>Desa Tanjungwangi</t>
+  </si>
+  <si>
+    <t>Cikalongwetan</t>
+  </si>
+  <si>
+    <t>Desa Cikalong</t>
+  </si>
+  <si>
+    <t>Desa Cipada</t>
+  </si>
+  <si>
+    <t>Desa Ciptagumati</t>
+  </si>
+  <si>
+    <t>Desa Cisomang Barat</t>
+  </si>
+  <si>
+    <t>Desa Ganjarsari</t>
+  </si>
+  <si>
+    <t>Desa Kanangasari</t>
+  </si>
+  <si>
+    <t>Desa Mandalamukti</t>
+  </si>
+  <si>
+    <t>Desa Mandalasari</t>
+  </si>
+  <si>
+    <t>Desa Mekarjaya</t>
+  </si>
+  <si>
+    <t>Desa Puteran</t>
+  </si>
+  <si>
+    <t>Desa Rende</t>
+  </si>
+  <si>
+    <t>Desa Tenjolaut</t>
+  </si>
+  <si>
+    <t>Desa Wangunjaya</t>
+  </si>
+  <si>
+    <t>Cililin</t>
+  </si>
+  <si>
+    <t>Desa Batulayang</t>
+  </si>
+  <si>
+    <t>Desa Budiharja</t>
+  </si>
+  <si>
+    <t>Desa Cililin</t>
+  </si>
+  <si>
+    <t>Desa Karanganyar</t>
+  </si>
+  <si>
+    <t>Desa Karangtanjung</t>
+  </si>
+  <si>
+    <t>Desa Karyamukti</t>
+  </si>
+  <si>
+    <t>Desa Kidangpananjung</t>
+  </si>
+  <si>
+    <t>Desa Mukapayung</t>
+  </si>
+  <si>
+    <t>Desa Nangerang</t>
+  </si>
+  <si>
+    <t>Desa Rancapanggung</t>
+  </si>
+  <si>
+    <t>Cipatat</t>
+  </si>
+  <si>
+    <t>Desa Cipatat</t>
+  </si>
+  <si>
+    <t>Desa Ciptaharja</t>
+  </si>
+  <si>
+    <t>Desa Cirawamekar</t>
+  </si>
+  <si>
+    <t>Desa Citatah</t>
+  </si>
+  <si>
+    <t>Desa Gunungmasigit</t>
+  </si>
+  <si>
+    <t>Desa Kertamukti</t>
+  </si>
+  <si>
+    <t>Desa Mandalawangi</t>
+  </si>
+  <si>
+    <t>Desa Nyalindung</t>
+  </si>
+  <si>
+    <t>Desa Sarimukti</t>
+  </si>
+  <si>
+    <t>Desa Sumurbandung</t>
+  </si>
+  <si>
+    <t>Rajamandala Kulon</t>
+  </si>
+  <si>
+    <t>Cipeundeuy</t>
+  </si>
+  <si>
+    <t>Desa Bojongmekar</t>
+  </si>
+  <si>
+    <t>Desa Ciharashas</t>
+  </si>
+  <si>
+    <t>Desa Cipeundeuy</t>
+  </si>
+  <si>
+    <t>Desa Ciroyom</t>
+  </si>
+  <si>
+    <t>Desa Jatimekar</t>
+  </si>
+  <si>
+    <t>Desa Margalaksana</t>
+  </si>
+  <si>
+    <t>Desa Margaluyu</t>
+  </si>
+  <si>
+    <t>Desa Nanggeleng</t>
+  </si>
+  <si>
+    <t>Desa Nyenang</t>
+  </si>
+  <si>
+    <t>Desa Sirnagalih</t>
+  </si>
+  <si>
+    <t>Desa Sirnaraja</t>
+  </si>
+  <si>
+    <t>Desa Sukahaji</t>
+  </si>
+  <si>
+    <t>Cipongkor</t>
+  </si>
+  <si>
+    <t>Desa Baranang Siang</t>
+  </si>
+  <si>
+    <t>Desa Cibenda</t>
+  </si>
+  <si>
+    <t>Desa Cijambu</t>
+  </si>
+  <si>
+    <t>Desa Cijenuk</t>
+  </si>
+  <si>
+    <t>Desa Cintaasih</t>
+  </si>
+  <si>
+    <t>Desa Citalem</t>
+  </si>
+  <si>
+    <t>Desa Girimukti</t>
+  </si>
+  <si>
+    <t>Desa Karangsari</t>
+  </si>
+  <si>
+    <t>Desa Mekarsari</t>
+  </si>
+  <si>
+    <t>Desa Neglasari</t>
+  </si>
+  <si>
+    <t>Desa Sarinagen</t>
+  </si>
+  <si>
+    <t>Desa Sukamulya</t>
+  </si>
+  <si>
+    <t>Cisarua</t>
+  </si>
+  <si>
+    <t>Desa Jambudipa</t>
+  </si>
+  <si>
+    <t>Desa Kertawangi</t>
+  </si>
+  <si>
+    <t>Desa Padaasih</t>
+  </si>
+  <si>
+    <t>Desa Pasirhalang</t>
+  </si>
+  <si>
+    <t>Desa Pasirlangu</t>
+  </si>
+  <si>
+    <t>Desa Sadangmekar</t>
+  </si>
+  <si>
+    <t>Desa Tugumukti</t>
+  </si>
+  <si>
+    <t>Gununghalu</t>
+  </si>
+  <si>
+    <t>Desa Bunijaya</t>
+  </si>
+  <si>
+    <t>Desa Celak</t>
+  </si>
+  <si>
+    <t>Desa Cilangari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>Desa Gununghalu</t>
+  </si>
+  <si>
+    <t>Desa SIndangjaya</t>
+  </si>
+  <si>
+    <t>Desa Sirnajaya</t>
+  </si>
+  <si>
+    <t>Desa Sukasari</t>
+  </si>
+  <si>
+    <t>Desa Tamanjaya</t>
+  </si>
+  <si>
+    <t>Desa Wargasaluyu</t>
+  </si>
+  <si>
+    <t>Lembang</t>
+  </si>
+  <si>
+    <t>Desa Cibodas</t>
+  </si>
+  <si>
+    <t>Desa Cibogo</t>
+  </si>
+  <si>
+    <t>Desa Cikahuripan</t>
+  </si>
+  <si>
+    <t>Desa Cikidang</t>
+  </si>
+  <si>
+    <t>Desa Cikoke</t>
+  </si>
+  <si>
+    <t>Desa Gudangkahuripan</t>
+  </si>
+  <si>
+    <t>Desa Jayagiri</t>
+  </si>
+  <si>
+    <t>Desa Kayuambon</t>
+  </si>
+  <si>
+    <t>Desa Langensari</t>
+  </si>
+  <si>
+    <t>Desa Lembang</t>
+  </si>
+  <si>
+    <t>Desa Mekarwangi</t>
+  </si>
+  <si>
+    <t>Desa Pagerwangi</t>
+  </si>
+  <si>
+    <t>Desa Sukajaya</t>
+  </si>
+  <si>
+    <t>Desa Suntenjaya</t>
+  </si>
+  <si>
+    <t>Desa Wangunharja</t>
+  </si>
+  <si>
+    <t>Desa Wangunsari</t>
+  </si>
+  <si>
+    <t>Ngamprah</t>
+  </si>
+  <si>
+    <t>Desa Bojongkoneng</t>
+  </si>
+  <si>
+    <t>Desa Cilame</t>
+  </si>
+  <si>
+    <t>Desa Cimanggu</t>
+  </si>
+  <si>
+    <t>Desa Gadobangkong</t>
+  </si>
+  <si>
+    <t>Desa Ngamprah</t>
+  </si>
+  <si>
+    <t>Desa Pakuhaji</t>
+  </si>
+  <si>
+    <t>Desa Sukatani</t>
+  </si>
+  <si>
+    <t>Padalarang</t>
+  </si>
+  <si>
+    <t>Desa Campakamekar</t>
+  </si>
+  <si>
+    <t>Desa Ciburuy</t>
+  </si>
+  <si>
+    <t>Desa Jayamekar</t>
+  </si>
+  <si>
+    <t>Desa Kertajaya</t>
+  </si>
+  <si>
+    <t>Desa Kertamulya</t>
+  </si>
+  <si>
+    <t>Desa Laksanamekar</t>
+  </si>
+  <si>
+    <t>Desa Padalarang</t>
+  </si>
+  <si>
+    <t>Desa Tagogapu</t>
+  </si>
+  <si>
+    <t>Parongpong</t>
+  </si>
+  <si>
+    <t>Desa Cigugurgirang</t>
+  </si>
+  <si>
+    <t>Desa Cihanjuang</t>
+  </si>
+  <si>
+    <t>Desa Cihanjuang Rahayu</t>
+  </si>
+  <si>
+    <t>Desa Cihideung</t>
+  </si>
+  <si>
+    <t>Desa Ciwaruga</t>
+  </si>
+  <si>
+    <t>Desa Karyawangi</t>
+  </si>
+  <si>
+    <t>Desa Sariwangi</t>
+  </si>
+  <si>
+    <t>Rongga</t>
+  </si>
+  <si>
+    <t>Desa Bojong</t>
+  </si>
+  <si>
+    <t>Desa Bojongsalam</t>
+  </si>
+  <si>
+    <t>Desa Cibedug</t>
+  </si>
+  <si>
+    <t>Desa Cibitung</t>
+  </si>
+  <si>
+    <t>Desa Cicadas</t>
+  </si>
+  <si>
+    <t>Desa Cinengah</t>
+  </si>
+  <si>
+    <t>Desa Sukamanah</t>
+  </si>
+  <si>
+    <t>Desa Sukaresmi</t>
+  </si>
+  <si>
+    <t>Saguling</t>
+  </si>
+  <si>
+    <t>Desa Bojonghaleuang</t>
+  </si>
+  <si>
+    <t>Desa Cikande</t>
+  </si>
+  <si>
+    <t>Desa Cipangeran</t>
+  </si>
+  <si>
+    <t>Desa Jati</t>
+  </si>
+  <si>
+    <t>Desa Saguling</t>
+  </si>
+  <si>
+    <t>Sindangkerta</t>
+  </si>
+  <si>
+    <t>Desa Bunianagara</t>
+  </si>
+  <si>
+    <t>Desa Cicangkanggirang</t>
+  </si>
+  <si>
+    <t>Desa Cikadu</t>
+  </si>
+  <si>
+    <t>Desa Cintakarya</t>
+  </si>
+  <si>
+    <t>Desa Pasirpogor</t>
+  </si>
+  <si>
+    <t>Desa Puncaksari</t>
+  </si>
+  <si>
+    <t>Desa Rancasenggang</t>
+  </si>
+  <si>
+    <t>Desa Sindangkerta</t>
+  </si>
+  <si>
+    <t>Desa Weninggalih</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -82,7 +582,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -90,12 +590,82 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -114,8 +684,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5DB47FA0-E2DF-4EDA-8547-B333035AAE03}" name="Tabel1" displayName="Tabel1" ref="A1:H6" totalsRowShown="0">
-  <autoFilter ref="A1:H6" xr:uid="{5DB47FA0-E2DF-4EDA-8547-B333035AAE03}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5DB47FA0-E2DF-4EDA-8547-B333035AAE03}" name="Tabel1" displayName="Tabel1" ref="A1:H152" totalsRowShown="0">
+  <autoFilter ref="A1:H152" xr:uid="{5DB47FA0-E2DF-4EDA-8547-B333035AAE03}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{5A442DD1-4F63-44B2-B5E2-C1DB8C2A2E6B}" name="ancaman"/>
     <tableColumn id="2" xr3:uid="{6724B160-8492-4C08-AFAA-6B6295A9173C}" name="kecamatan"/>
@@ -427,7 +997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01A703C3-5000-470B-AACB-063DF88ABEDC}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" customWidth="1"/>
@@ -440,7 +1010,7 @@
     <col min="8" max="8" width="11.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -464,6 +1034,3479 @@
       </c>
       <c r="H1" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3">
+        <v>113</v>
+      </c>
+      <c r="E2" s="3">
+        <v>58</v>
+      </c>
+      <c r="F2" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="6">
+        <v>3.1459999999999999</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1.577</v>
+      </c>
+      <c r="F3" s="6">
+        <v>190</v>
+      </c>
+      <c r="G3" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="6">
+        <v>1.869</v>
+      </c>
+      <c r="E4" s="6">
+        <v>938</v>
+      </c>
+      <c r="F4" s="6">
+        <v>161</v>
+      </c>
+      <c r="G4" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="6">
+        <v>2.9460000000000002</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1.464</v>
+      </c>
+      <c r="F5" s="6">
+        <v>277</v>
+      </c>
+      <c r="G5" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="6">
+        <v>2.2280000000000002</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1.1240000000000001</v>
+      </c>
+      <c r="F8" s="6">
+        <v>183</v>
+      </c>
+      <c r="G8" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="6">
+        <v>2.968</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1.526</v>
+      </c>
+      <c r="F9" s="6">
+        <v>313</v>
+      </c>
+      <c r="G9" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="6">
+        <v>6.7960000000000003</v>
+      </c>
+      <c r="E10" s="6">
+        <v>3.601</v>
+      </c>
+      <c r="F10" s="6">
+        <v>801</v>
+      </c>
+      <c r="G10" s="6">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1.625</v>
+      </c>
+      <c r="E11" s="6">
+        <v>875</v>
+      </c>
+      <c r="F11" s="6">
+        <v>172</v>
+      </c>
+      <c r="G11" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="6">
+        <v>3.1840000000000002</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1.6879999999999999</v>
+      </c>
+      <c r="F12" s="6">
+        <v>316</v>
+      </c>
+      <c r="G12" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="6">
+        <v>6.8689999999999998</v>
+      </c>
+      <c r="E13" s="6">
+        <v>3.9119999999999999</v>
+      </c>
+      <c r="F13" s="6">
+        <v>622</v>
+      </c>
+      <c r="G13" s="6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="6">
+        <v>2.589</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1.4039999999999999</v>
+      </c>
+      <c r="F14" s="6">
+        <v>268</v>
+      </c>
+      <c r="G14" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="6">
+        <v>1.468</v>
+      </c>
+      <c r="E15" s="6">
+        <v>787</v>
+      </c>
+      <c r="F15" s="6">
+        <v>188</v>
+      </c>
+      <c r="G15" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="6">
+        <v>7.6260000000000003</v>
+      </c>
+      <c r="E16" s="6">
+        <v>4.3550000000000004</v>
+      </c>
+      <c r="F16" s="6">
+        <v>719</v>
+      </c>
+      <c r="G16" s="6">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="6">
+        <v>3.59</v>
+      </c>
+      <c r="E17" s="6">
+        <v>2.17</v>
+      </c>
+      <c r="F17" s="6">
+        <v>417</v>
+      </c>
+      <c r="G17" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="6">
+        <v>5.9619999999999997</v>
+      </c>
+      <c r="E18" s="6">
+        <v>3.177</v>
+      </c>
+      <c r="F18" s="6">
+        <v>624</v>
+      </c>
+      <c r="G18" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="6">
+        <v>5.3819999999999997</v>
+      </c>
+      <c r="E19" s="6">
+        <v>2.8439999999999999</v>
+      </c>
+      <c r="F19" s="6">
+        <v>642</v>
+      </c>
+      <c r="G19" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="6">
+        <v>9.2520000000000007</v>
+      </c>
+      <c r="E20" s="6">
+        <v>4.835</v>
+      </c>
+      <c r="F20" s="6">
+        <v>728</v>
+      </c>
+      <c r="G20" s="6">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="6">
+        <v>3.2120000000000002</v>
+      </c>
+      <c r="E21" s="6">
+        <v>1.845</v>
+      </c>
+      <c r="F21" s="6">
+        <v>350</v>
+      </c>
+      <c r="G21" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="6">
+        <v>4.5350000000000001</v>
+      </c>
+      <c r="E22" s="6">
+        <v>2.52</v>
+      </c>
+      <c r="F22" s="6">
+        <v>450</v>
+      </c>
+      <c r="G22" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="6">
+        <v>3.3519999999999999</v>
+      </c>
+      <c r="E23" s="6">
+        <v>1.835</v>
+      </c>
+      <c r="F23" s="6">
+        <v>430</v>
+      </c>
+      <c r="G23" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="6">
+        <v>2.101</v>
+      </c>
+      <c r="E24" s="6">
+        <v>1.131</v>
+      </c>
+      <c r="F24" s="6">
+        <v>252</v>
+      </c>
+      <c r="G24" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="6">
+        <v>7.4249999999999998</v>
+      </c>
+      <c r="E25" s="6">
+        <v>4.0620000000000003</v>
+      </c>
+      <c r="F25" s="6">
+        <v>925</v>
+      </c>
+      <c r="G25" s="6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="6">
+        <v>421</v>
+      </c>
+      <c r="E26" s="6">
+        <v>242</v>
+      </c>
+      <c r="F26" s="6">
+        <v>57</v>
+      </c>
+      <c r="G26" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="6">
+        <v>611</v>
+      </c>
+      <c r="E27" s="6">
+        <v>324</v>
+      </c>
+      <c r="F27" s="6">
+        <v>69</v>
+      </c>
+      <c r="G27" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="6">
+        <v>3.5819999999999999</v>
+      </c>
+      <c r="E28" s="6">
+        <v>2.089</v>
+      </c>
+      <c r="F28" s="6">
+        <v>373</v>
+      </c>
+      <c r="G28" s="6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="6">
+        <v>6.0579999999999998</v>
+      </c>
+      <c r="E29" s="6">
+        <v>3.16</v>
+      </c>
+      <c r="F29" s="6">
+        <v>705</v>
+      </c>
+      <c r="G29" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="6">
+        <v>4.08</v>
+      </c>
+      <c r="E30" s="6">
+        <v>2.238</v>
+      </c>
+      <c r="F30" s="6">
+        <v>397</v>
+      </c>
+      <c r="G30" s="6">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" s="6">
+        <v>4.1020000000000003</v>
+      </c>
+      <c r="E31" s="6">
+        <v>2.2509999999999999</v>
+      </c>
+      <c r="F31" s="6">
+        <v>598</v>
+      </c>
+      <c r="G31" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" s="6">
+        <v>11.14</v>
+      </c>
+      <c r="E32" s="6">
+        <v>6.3129999999999997</v>
+      </c>
+      <c r="F32" s="6">
+        <v>1.198</v>
+      </c>
+      <c r="G32" s="6">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="6">
+        <v>4.8079999999999998</v>
+      </c>
+      <c r="E33" s="6">
+        <v>2.714</v>
+      </c>
+      <c r="F33" s="6">
+        <v>416</v>
+      </c>
+      <c r="G33" s="6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" s="6">
+        <v>3.145</v>
+      </c>
+      <c r="E34" s="6">
+        <v>1.75</v>
+      </c>
+      <c r="F34" s="6">
+        <v>309</v>
+      </c>
+      <c r="G34" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D35" s="6">
+        <v>1.7709999999999999</v>
+      </c>
+      <c r="E35" s="6">
+        <v>951</v>
+      </c>
+      <c r="F35" s="6">
+        <v>180</v>
+      </c>
+      <c r="G35" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D36" s="6">
+        <v>1.327</v>
+      </c>
+      <c r="E36" s="6">
+        <v>698</v>
+      </c>
+      <c r="F36" s="6">
+        <v>144</v>
+      </c>
+      <c r="G36" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D37" s="6">
+        <v>5.109</v>
+      </c>
+      <c r="E37" s="6">
+        <v>2.7149999999999999</v>
+      </c>
+      <c r="F37" s="6">
+        <v>552</v>
+      </c>
+      <c r="G37" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38" s="6">
+        <v>12.673</v>
+      </c>
+      <c r="E38" s="6">
+        <v>6.8520000000000003</v>
+      </c>
+      <c r="F38" s="6">
+        <v>1.282</v>
+      </c>
+      <c r="G38" s="6">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39" s="6">
+        <v>12.634</v>
+      </c>
+      <c r="E39" s="6">
+        <v>6.6150000000000002</v>
+      </c>
+      <c r="F39" s="6">
+        <v>1.2390000000000001</v>
+      </c>
+      <c r="G39" s="6">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40" s="6">
+        <v>2.6160000000000001</v>
+      </c>
+      <c r="E40" s="6">
+        <v>1.462</v>
+      </c>
+      <c r="F40" s="6">
+        <v>309</v>
+      </c>
+      <c r="G40" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41" s="6">
+        <v>363</v>
+      </c>
+      <c r="E41" s="6">
+        <v>201</v>
+      </c>
+      <c r="F41" s="6">
+        <v>37</v>
+      </c>
+      <c r="G41" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" s="6">
+        <v>384</v>
+      </c>
+      <c r="E42" s="6">
+        <v>213</v>
+      </c>
+      <c r="F42" s="6">
+        <v>40</v>
+      </c>
+      <c r="G42" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D43" s="6">
+        <v>4.5709999999999997</v>
+      </c>
+      <c r="E43" s="6">
+        <v>2.444</v>
+      </c>
+      <c r="F43" s="6">
+        <v>481</v>
+      </c>
+      <c r="G43" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D44" s="6">
+        <v>1.8759999999999999</v>
+      </c>
+      <c r="E44" s="6">
+        <v>1.0129999999999999</v>
+      </c>
+      <c r="F44" s="6">
+        <v>197</v>
+      </c>
+      <c r="G44" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D45" s="6">
+        <v>6.7039999999999997</v>
+      </c>
+      <c r="E45" s="6">
+        <v>3.5859999999999999</v>
+      </c>
+      <c r="F45" s="6">
+        <v>821</v>
+      </c>
+      <c r="G45" s="6">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" s="6">
+        <v>1.0309999999999999</v>
+      </c>
+      <c r="E46" s="6">
+        <v>585</v>
+      </c>
+      <c r="F46" s="6">
+        <v>119</v>
+      </c>
+      <c r="G46" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D47" s="6">
+        <v>273</v>
+      </c>
+      <c r="E47" s="6">
+        <v>153</v>
+      </c>
+      <c r="F47" s="6">
+        <v>25</v>
+      </c>
+      <c r="G47" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D48" s="6">
+        <v>963</v>
+      </c>
+      <c r="E48" s="6">
+        <v>545</v>
+      </c>
+      <c r="F48" s="6">
+        <v>91</v>
+      </c>
+      <c r="G48" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D49" s="6">
+        <v>316</v>
+      </c>
+      <c r="E49" s="6">
+        <v>175</v>
+      </c>
+      <c r="F49" s="6">
+        <v>30</v>
+      </c>
+      <c r="G49" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D50" s="6">
+        <v>895</v>
+      </c>
+      <c r="E50" s="6">
+        <v>487</v>
+      </c>
+      <c r="F50" s="6">
+        <v>86</v>
+      </c>
+      <c r="G50" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D51" s="6">
+        <v>584</v>
+      </c>
+      <c r="E51" s="6">
+        <v>342</v>
+      </c>
+      <c r="F51" s="6">
+        <v>64</v>
+      </c>
+      <c r="G51" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D52" s="6">
+        <v>131</v>
+      </c>
+      <c r="E52" s="6">
+        <v>73</v>
+      </c>
+      <c r="F52" s="6">
+        <v>16</v>
+      </c>
+      <c r="G52" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D53" s="6">
+        <v>1.4039999999999999</v>
+      </c>
+      <c r="E53" s="6">
+        <v>810</v>
+      </c>
+      <c r="F53" s="6">
+        <v>147</v>
+      </c>
+      <c r="G53" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D54" s="6">
+        <v>973</v>
+      </c>
+      <c r="E54" s="6">
+        <v>574</v>
+      </c>
+      <c r="F54" s="6">
+        <v>120</v>
+      </c>
+      <c r="G54" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D55" s="6">
+        <v>406</v>
+      </c>
+      <c r="E55" s="6">
+        <v>230</v>
+      </c>
+      <c r="F55" s="6">
+        <v>43</v>
+      </c>
+      <c r="G55" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D56" s="6">
+        <v>370</v>
+      </c>
+      <c r="E56" s="6">
+        <v>204</v>
+      </c>
+      <c r="F56" s="6">
+        <v>47</v>
+      </c>
+      <c r="G56" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D57" s="6">
+        <v>531</v>
+      </c>
+      <c r="E57" s="6">
+        <v>310</v>
+      </c>
+      <c r="F57" s="6">
+        <v>55</v>
+      </c>
+      <c r="G57" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D58" s="6">
+        <v>35</v>
+      </c>
+      <c r="E58" s="6">
+        <v>19</v>
+      </c>
+      <c r="F58" s="6">
+        <v>4</v>
+      </c>
+      <c r="G58" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D59" s="6">
+        <v>7.0179999999999998</v>
+      </c>
+      <c r="E59" s="6">
+        <v>3.8660000000000001</v>
+      </c>
+      <c r="F59" s="6">
+        <v>684</v>
+      </c>
+      <c r="G59" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D60" s="6">
+        <v>4.968</v>
+      </c>
+      <c r="E60" s="6">
+        <v>3.0409999999999999</v>
+      </c>
+      <c r="F60" s="6">
+        <v>438</v>
+      </c>
+      <c r="G60" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D61" s="6">
+        <v>3.169</v>
+      </c>
+      <c r="E61" s="6">
+        <v>1.8160000000000001</v>
+      </c>
+      <c r="F61" s="6">
+        <v>302</v>
+      </c>
+      <c r="G61" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D62" s="6">
+        <v>4.6959999999999997</v>
+      </c>
+      <c r="E62" s="6">
+        <v>2.6110000000000002</v>
+      </c>
+      <c r="F62" s="6">
+        <v>531</v>
+      </c>
+      <c r="G62" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D63" s="6">
+        <v>6.5060000000000002</v>
+      </c>
+      <c r="E63" s="6">
+        <v>3.85</v>
+      </c>
+      <c r="F63" s="6">
+        <v>607</v>
+      </c>
+      <c r="G63" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D64" s="6">
+        <v>2.855</v>
+      </c>
+      <c r="E64" s="6">
+        <v>1.591</v>
+      </c>
+      <c r="F64" s="6">
+        <v>300</v>
+      </c>
+      <c r="G64" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D65" s="6">
+        <v>5.8810000000000002</v>
+      </c>
+      <c r="E65" s="6">
+        <v>3.2639999999999998</v>
+      </c>
+      <c r="F65" s="6">
+        <v>771</v>
+      </c>
+      <c r="G65" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D66" s="6">
+        <v>4.5830000000000002</v>
+      </c>
+      <c r="E66" s="6">
+        <v>2.7850000000000001</v>
+      </c>
+      <c r="F66" s="6">
+        <v>527</v>
+      </c>
+      <c r="G66" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D67" s="6">
+        <v>297</v>
+      </c>
+      <c r="E67" s="6">
+        <v>176</v>
+      </c>
+      <c r="F67" s="6">
+        <v>38</v>
+      </c>
+      <c r="G67" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D68" s="6">
+        <v>4.0949999999999998</v>
+      </c>
+      <c r="E68" s="6">
+        <v>2.3540000000000001</v>
+      </c>
+      <c r="F68" s="6">
+        <v>451</v>
+      </c>
+      <c r="G68" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D69" s="6">
+        <v>4.9989999999999997</v>
+      </c>
+      <c r="E69" s="6">
+        <v>2.883</v>
+      </c>
+      <c r="F69" s="6">
+        <v>496</v>
+      </c>
+      <c r="G69" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D70" s="6">
+        <v>3.4390000000000001</v>
+      </c>
+      <c r="E70" s="6">
+        <v>2.1440000000000001</v>
+      </c>
+      <c r="F70" s="6">
+        <v>235</v>
+      </c>
+      <c r="G70" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D71" s="6">
+        <v>666</v>
+      </c>
+      <c r="E71" s="6">
+        <v>380</v>
+      </c>
+      <c r="F71" s="6">
+        <v>85</v>
+      </c>
+      <c r="G71" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D72" s="6">
+        <v>4.9429999999999996</v>
+      </c>
+      <c r="E72" s="6">
+        <v>2.6339999999999999</v>
+      </c>
+      <c r="F72" s="6">
+        <v>411</v>
+      </c>
+      <c r="G72" s="6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D73" s="6">
+        <v>12.315</v>
+      </c>
+      <c r="E73" s="6">
+        <v>6.38</v>
+      </c>
+      <c r="F73" s="6">
+        <v>903</v>
+      </c>
+      <c r="G73" s="6">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D74" s="6">
+        <v>3.2309999999999999</v>
+      </c>
+      <c r="E74" s="6">
+        <v>1.6379999999999999</v>
+      </c>
+      <c r="F74" s="6">
+        <v>282</v>
+      </c>
+      <c r="G74" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D75" s="6">
+        <v>4.8220000000000001</v>
+      </c>
+      <c r="E75" s="6">
+        <v>2.5880000000000001</v>
+      </c>
+      <c r="F75" s="6">
+        <v>357</v>
+      </c>
+      <c r="G75" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D76" s="6">
+        <v>4.4080000000000004</v>
+      </c>
+      <c r="E76" s="6">
+        <v>2.4319999999999999</v>
+      </c>
+      <c r="F76" s="6">
+        <v>350</v>
+      </c>
+      <c r="G76" s="6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D77" s="6">
+        <v>3.0470000000000002</v>
+      </c>
+      <c r="E77" s="6">
+        <v>1.5940000000000001</v>
+      </c>
+      <c r="F77" s="6">
+        <v>240</v>
+      </c>
+      <c r="G77" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D78" s="6">
+        <v>6.0919999999999996</v>
+      </c>
+      <c r="E78" s="6">
+        <v>3.2130000000000001</v>
+      </c>
+      <c r="F78" s="6">
+        <v>598</v>
+      </c>
+      <c r="G78" s="6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D79" s="6">
+        <v>3.5750000000000002</v>
+      </c>
+      <c r="E79" s="6">
+        <v>1.952</v>
+      </c>
+      <c r="F79" s="6">
+        <v>389</v>
+      </c>
+      <c r="G79" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D80" s="6">
+        <v>4.5629999999999997</v>
+      </c>
+      <c r="E80" s="6">
+        <v>2.5419999999999998</v>
+      </c>
+      <c r="F80" s="6">
+        <v>507</v>
+      </c>
+      <c r="G80" s="6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A81" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D81" s="6">
+        <v>5.5759999999999996</v>
+      </c>
+      <c r="E81" s="6">
+        <v>3.1280000000000001</v>
+      </c>
+      <c r="F81" s="6">
+        <v>648</v>
+      </c>
+      <c r="G81" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D82" s="6">
+        <v>7.0670000000000002</v>
+      </c>
+      <c r="E82" s="6">
+        <v>4.0209999999999999</v>
+      </c>
+      <c r="F82" s="6">
+        <v>785</v>
+      </c>
+      <c r="G82" s="6">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D83" s="6">
+        <v>7.0250000000000004</v>
+      </c>
+      <c r="E83" s="6">
+        <v>3.964</v>
+      </c>
+      <c r="F83" s="6">
+        <v>878</v>
+      </c>
+      <c r="G83" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D84" s="6">
+        <v>3.1459999999999999</v>
+      </c>
+      <c r="E84" s="6">
+        <v>1.7689999999999999</v>
+      </c>
+      <c r="F84" s="6">
+        <v>317</v>
+      </c>
+      <c r="G84" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A85" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D85" s="6">
+        <v>7.0389999999999997</v>
+      </c>
+      <c r="E85" s="6">
+        <v>3.948</v>
+      </c>
+      <c r="F85" s="6">
+        <v>754</v>
+      </c>
+      <c r="G85" s="6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A86" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D86" s="6">
+        <v>5.29</v>
+      </c>
+      <c r="E86" s="6">
+        <v>2.948</v>
+      </c>
+      <c r="F86" s="6">
+        <v>486</v>
+      </c>
+      <c r="G86" s="6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A87" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D87" s="6">
+        <v>7.9130000000000003</v>
+      </c>
+      <c r="E87" s="6">
+        <v>4.5330000000000004</v>
+      </c>
+      <c r="F87" s="6">
+        <v>734</v>
+      </c>
+      <c r="G87" s="6">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A88" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D88" s="6">
+        <v>6.5419999999999998</v>
+      </c>
+      <c r="E88" s="6">
+        <v>3.6779999999999999</v>
+      </c>
+      <c r="F88" s="6">
+        <v>745</v>
+      </c>
+      <c r="G88" s="6">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A89" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D89" s="6">
+        <v>3.2509999999999999</v>
+      </c>
+      <c r="E89" s="6">
+        <v>1.7330000000000001</v>
+      </c>
+      <c r="F89" s="6">
+        <v>341</v>
+      </c>
+      <c r="G89" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A90" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D90" s="6">
+        <v>4.01</v>
+      </c>
+      <c r="E90" s="6">
+        <v>2.113</v>
+      </c>
+      <c r="F90" s="6">
+        <v>303</v>
+      </c>
+      <c r="G90" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A91" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D91" s="6">
+        <v>3.8839999999999999</v>
+      </c>
+      <c r="E91" s="6">
+        <v>1.9770000000000001</v>
+      </c>
+      <c r="F91" s="6">
+        <v>344</v>
+      </c>
+      <c r="G91" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A92" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D92" s="6">
+        <v>2.41</v>
+      </c>
+      <c r="E92" s="6">
+        <v>1.2509999999999999</v>
+      </c>
+      <c r="F92" s="6">
+        <v>287</v>
+      </c>
+      <c r="G92" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A93" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D93" s="6">
+        <v>3.6819999999999999</v>
+      </c>
+      <c r="E93" s="6">
+        <v>1.8680000000000001</v>
+      </c>
+      <c r="F93" s="6">
+        <v>263</v>
+      </c>
+      <c r="G93" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A94" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D94" s="6">
+        <v>9.8390000000000004</v>
+      </c>
+      <c r="E94" s="6">
+        <v>4.9690000000000003</v>
+      </c>
+      <c r="F94" s="6">
+        <v>660</v>
+      </c>
+      <c r="G94" s="6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A95" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D95" s="6">
+        <v>9.82</v>
+      </c>
+      <c r="E95" s="6">
+        <v>5.0259999999999998</v>
+      </c>
+      <c r="F95" s="6">
+        <v>846</v>
+      </c>
+      <c r="G95" s="6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A96" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D96" s="6">
+        <v>157</v>
+      </c>
+      <c r="E96" s="6">
+        <v>80</v>
+      </c>
+      <c r="F96" s="6">
+        <v>11</v>
+      </c>
+      <c r="G96" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A97" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D97" s="6">
+        <v>3.6160000000000001</v>
+      </c>
+      <c r="E97" s="6">
+        <v>1.835</v>
+      </c>
+      <c r="F97" s="6">
+        <v>295</v>
+      </c>
+      <c r="G97" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A98" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D98" s="6">
+        <v>3.379</v>
+      </c>
+      <c r="E98" s="6">
+        <v>1.7749999999999999</v>
+      </c>
+      <c r="F98" s="6">
+        <v>181</v>
+      </c>
+      <c r="G98" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A99" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D99" s="6">
+        <v>5.8049999999999997</v>
+      </c>
+      <c r="E99" s="6">
+        <v>3.1659999999999999</v>
+      </c>
+      <c r="F99" s="6">
+        <v>847</v>
+      </c>
+      <c r="G99" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A100" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D100" s="6">
+        <v>8.0960000000000001</v>
+      </c>
+      <c r="E100" s="6">
+        <v>4.1369999999999996</v>
+      </c>
+      <c r="F100" s="6">
+        <v>735</v>
+      </c>
+      <c r="G100" s="6">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A101" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D101" s="6">
+        <v>3.121</v>
+      </c>
+      <c r="E101" s="6">
+        <v>1.5880000000000001</v>
+      </c>
+      <c r="F101" s="6">
+        <v>293</v>
+      </c>
+      <c r="G101" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A102" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D102" s="6">
+        <v>8.4700000000000006</v>
+      </c>
+      <c r="E102" s="6">
+        <v>4.46</v>
+      </c>
+      <c r="F102" s="6">
+        <v>1.01</v>
+      </c>
+      <c r="G102" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A103" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D103" s="6">
+        <v>1.222</v>
+      </c>
+      <c r="E103" s="6">
+        <v>628</v>
+      </c>
+      <c r="F103" s="6">
+        <v>131</v>
+      </c>
+      <c r="G103" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A104" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D104" s="6">
+        <v>6.7439999999999998</v>
+      </c>
+      <c r="E104" s="6">
+        <v>3.532</v>
+      </c>
+      <c r="F104" s="6">
+        <v>628</v>
+      </c>
+      <c r="G104" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A105" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D105" s="6">
+        <v>11.792</v>
+      </c>
+      <c r="E105" s="6">
+        <v>6.5709999999999997</v>
+      </c>
+      <c r="F105" s="6">
+        <v>1.129</v>
+      </c>
+      <c r="G105" s="6">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A106" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D106" s="6">
+        <v>3.2909999999999999</v>
+      </c>
+      <c r="E106" s="6">
+        <v>1.526</v>
+      </c>
+      <c r="F106" s="6">
+        <v>177</v>
+      </c>
+      <c r="G106" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A107" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D107" s="6">
+        <v>5.7030000000000003</v>
+      </c>
+      <c r="E107" s="6">
+        <v>3.4119999999999999</v>
+      </c>
+      <c r="F107" s="6">
+        <v>607</v>
+      </c>
+      <c r="G107" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A108" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D108" s="6">
+        <v>373</v>
+      </c>
+      <c r="E108" s="6">
+        <v>194</v>
+      </c>
+      <c r="F108" s="6">
+        <v>20</v>
+      </c>
+      <c r="G108" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A109" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D109" s="6">
+        <v>229</v>
+      </c>
+      <c r="E109" s="6">
+        <v>116</v>
+      </c>
+      <c r="F109" s="6">
+        <v>21</v>
+      </c>
+      <c r="G109" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A110" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D110" s="6">
+        <v>3.0779999999999998</v>
+      </c>
+      <c r="E110" s="6">
+        <v>1.702</v>
+      </c>
+      <c r="F110" s="6">
+        <v>237</v>
+      </c>
+      <c r="G110" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A111" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D111" s="6">
+        <v>2.9009999999999998</v>
+      </c>
+      <c r="E111" s="6">
+        <v>1.4510000000000001</v>
+      </c>
+      <c r="F111" s="6">
+        <v>281</v>
+      </c>
+      <c r="G111" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A112" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D112" s="6">
+        <v>2.0880000000000001</v>
+      </c>
+      <c r="E112" s="6">
+        <v>1.095</v>
+      </c>
+      <c r="F112" s="6">
+        <v>152</v>
+      </c>
+      <c r="G112" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A113" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D113" s="6">
+        <v>6.9960000000000004</v>
+      </c>
+      <c r="E113" s="6">
+        <v>3.6840000000000002</v>
+      </c>
+      <c r="F113" s="6">
+        <v>713</v>
+      </c>
+      <c r="G113" s="6">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A114" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D114" s="6">
+        <v>4.8470000000000004</v>
+      </c>
+      <c r="E114" s="6">
+        <v>2.508</v>
+      </c>
+      <c r="F114" s="6">
+        <v>364</v>
+      </c>
+      <c r="G114" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A115" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D115" s="6">
+        <v>10.486000000000001</v>
+      </c>
+      <c r="E115" s="6">
+        <v>5.2770000000000001</v>
+      </c>
+      <c r="F115" s="6">
+        <v>859</v>
+      </c>
+      <c r="G115" s="6">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A116" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D116" s="6">
+        <v>0</v>
+      </c>
+      <c r="E116" s="6">
+        <v>0</v>
+      </c>
+      <c r="F116" s="6">
+        <v>0</v>
+      </c>
+      <c r="G116" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A117" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D117" s="6">
+        <v>1.544</v>
+      </c>
+      <c r="E117" s="6">
+        <v>797</v>
+      </c>
+      <c r="F117" s="6">
+        <v>106</v>
+      </c>
+      <c r="G117" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A118" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D118" s="6">
+        <v>3.589</v>
+      </c>
+      <c r="E118" s="6">
+        <v>1.752</v>
+      </c>
+      <c r="F118" s="6">
+        <v>267</v>
+      </c>
+      <c r="G118" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A119" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D119" s="6">
+        <v>6.3460000000000001</v>
+      </c>
+      <c r="E119" s="6">
+        <v>3.0990000000000002</v>
+      </c>
+      <c r="F119" s="6">
+        <v>399</v>
+      </c>
+      <c r="G119" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A120" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D120" s="6">
+        <v>6.53</v>
+      </c>
+      <c r="E120" s="6">
+        <v>3.5739999999999998</v>
+      </c>
+      <c r="F120" s="6">
+        <v>616</v>
+      </c>
+      <c r="G120" s="6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A121" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D121" s="6">
+        <v>309</v>
+      </c>
+      <c r="E121" s="6">
+        <v>161</v>
+      </c>
+      <c r="F121" s="6">
+        <v>19</v>
+      </c>
+      <c r="G121" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A122" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D122" s="6">
+        <v>3.0939999999999999</v>
+      </c>
+      <c r="E122" s="6">
+        <v>1.5820000000000001</v>
+      </c>
+      <c r="F122" s="6">
+        <v>234</v>
+      </c>
+      <c r="G122" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A123" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D123" s="6">
+        <v>9.141</v>
+      </c>
+      <c r="E123" s="6">
+        <v>4.694</v>
+      </c>
+      <c r="F123" s="6">
+        <v>620</v>
+      </c>
+      <c r="G123" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A124" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D124" s="6">
+        <v>7.3150000000000004</v>
+      </c>
+      <c r="E124" s="6">
+        <v>3.6859999999999999</v>
+      </c>
+      <c r="F124" s="6">
+        <v>395</v>
+      </c>
+      <c r="G124" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A125" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D125" s="6">
+        <v>1.64</v>
+      </c>
+      <c r="E125" s="6">
+        <v>880</v>
+      </c>
+      <c r="F125" s="6">
+        <v>98</v>
+      </c>
+      <c r="G125" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A126" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D126" s="6">
+        <v>3.3279999999999998</v>
+      </c>
+      <c r="E126" s="6">
+        <v>1.649</v>
+      </c>
+      <c r="F126" s="6">
+        <v>249</v>
+      </c>
+      <c r="G126" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A127" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D127" s="6">
+        <v>2.4340000000000002</v>
+      </c>
+      <c r="E127" s="6">
+        <v>1.2210000000000001</v>
+      </c>
+      <c r="F127" s="6">
+        <v>149</v>
+      </c>
+      <c r="G127" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A128" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D128" s="6">
+        <v>1.679</v>
+      </c>
+      <c r="E128" s="6">
+        <v>984</v>
+      </c>
+      <c r="F128" s="6">
+        <v>151</v>
+      </c>
+      <c r="G128" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A129" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D129" s="6">
+        <v>4.3339999999999996</v>
+      </c>
+      <c r="E129" s="6">
+        <v>2.3290000000000002</v>
+      </c>
+      <c r="F129" s="6">
+        <v>388</v>
+      </c>
+      <c r="G129" s="6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A130" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D130" s="6">
+        <v>1.369</v>
+      </c>
+      <c r="E130" s="6">
+        <v>852</v>
+      </c>
+      <c r="F130" s="6">
+        <v>128</v>
+      </c>
+      <c r="G130" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A131" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D131" s="6">
+        <v>6.1189999999999998</v>
+      </c>
+      <c r="E131" s="6">
+        <v>3.4740000000000002</v>
+      </c>
+      <c r="F131" s="6">
+        <v>522</v>
+      </c>
+      <c r="G131" s="6">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A132" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D132" s="6">
+        <v>5.0730000000000004</v>
+      </c>
+      <c r="E132" s="6">
+        <v>2.9820000000000002</v>
+      </c>
+      <c r="F132" s="6">
+        <v>380</v>
+      </c>
+      <c r="G132" s="6">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A133" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D133" s="6">
+        <v>4.6870000000000003</v>
+      </c>
+      <c r="E133" s="6">
+        <v>2.7850000000000001</v>
+      </c>
+      <c r="F133" s="6">
+        <v>470</v>
+      </c>
+      <c r="G133" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A134" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D134" s="6">
+        <v>6.4550000000000001</v>
+      </c>
+      <c r="E134" s="6">
+        <v>3.726</v>
+      </c>
+      <c r="F134" s="6">
+        <v>623</v>
+      </c>
+      <c r="G134" s="6">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A135" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D135" s="6">
+        <v>9.0220000000000002</v>
+      </c>
+      <c r="E135" s="6">
+        <v>5.2729999999999997</v>
+      </c>
+      <c r="F135" s="6">
+        <v>681</v>
+      </c>
+      <c r="G135" s="6">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A136" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D136" s="6">
+        <v>1.589</v>
+      </c>
+      <c r="E136" s="6">
+        <v>830</v>
+      </c>
+      <c r="F136" s="6">
+        <v>164</v>
+      </c>
+      <c r="G136" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A137" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D137" s="6">
+        <v>1.6020000000000001</v>
+      </c>
+      <c r="E137" s="6">
+        <v>861</v>
+      </c>
+      <c r="F137" s="6">
+        <v>144</v>
+      </c>
+      <c r="G137" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A138" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D138" s="6">
+        <v>3.3370000000000002</v>
+      </c>
+      <c r="E138" s="6">
+        <v>1.9179999999999999</v>
+      </c>
+      <c r="F138" s="6">
+        <v>386</v>
+      </c>
+      <c r="G138" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A139" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D139" s="6">
+        <v>1.472</v>
+      </c>
+      <c r="E139" s="6">
+        <v>797</v>
+      </c>
+      <c r="F139" s="6">
+        <v>152</v>
+      </c>
+      <c r="G139" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A140" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D140" s="6">
+        <v>3.444</v>
+      </c>
+      <c r="E140" s="6">
+        <v>1.9930000000000001</v>
+      </c>
+      <c r="F140" s="6">
+        <v>475</v>
+      </c>
+      <c r="G140" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A141" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D141" s="6">
+        <v>6.5750000000000002</v>
+      </c>
+      <c r="E141" s="6">
+        <v>3.62</v>
+      </c>
+      <c r="F141" s="6">
+        <v>547</v>
+      </c>
+      <c r="G141" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A142" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D142" s="6">
+        <v>4.1749999999999998</v>
+      </c>
+      <c r="E142" s="6">
+        <v>2.492</v>
+      </c>
+      <c r="F142" s="6">
+        <v>485</v>
+      </c>
+      <c r="G142" s="6">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A143" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D143" s="6">
+        <v>7.9729999999999999</v>
+      </c>
+      <c r="E143" s="6">
+        <v>4.6710000000000003</v>
+      </c>
+      <c r="F143" s="6">
+        <v>892</v>
+      </c>
+      <c r="G143" s="6">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A144" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D144" s="6">
+        <v>1.7929999999999999</v>
+      </c>
+      <c r="E144" s="6">
+        <v>1.0760000000000001</v>
+      </c>
+      <c r="F144" s="6">
+        <v>200</v>
+      </c>
+      <c r="G144" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A145" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D145" s="6">
+        <v>2.11</v>
+      </c>
+      <c r="E145" s="6">
+        <v>1.2549999999999999</v>
+      </c>
+      <c r="F145" s="6">
+        <v>234</v>
+      </c>
+      <c r="G145" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A146" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D146" s="6">
+        <v>3.7330000000000001</v>
+      </c>
+      <c r="E146" s="6">
+        <v>2.073</v>
+      </c>
+      <c r="F146" s="6">
+        <v>259</v>
+      </c>
+      <c r="G146" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A147" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D147" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="E147" s="6">
+        <v>1.4370000000000001</v>
+      </c>
+      <c r="F147" s="6">
+        <v>283</v>
+      </c>
+      <c r="G147" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A148" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D148" s="6">
+        <v>2.105</v>
+      </c>
+      <c r="E148" s="6">
+        <v>1.2050000000000001</v>
+      </c>
+      <c r="F148" s="6">
+        <v>265</v>
+      </c>
+      <c r="G148" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A149" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D149" s="6">
+        <v>5.2320000000000002</v>
+      </c>
+      <c r="E149" s="6">
+        <v>3.0779999999999998</v>
+      </c>
+      <c r="F149" s="6">
+        <v>457</v>
+      </c>
+      <c r="G149" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A150" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D150" s="6">
+        <v>0</v>
+      </c>
+      <c r="E150" s="6">
+        <v>0</v>
+      </c>
+      <c r="F150" s="6">
+        <v>0</v>
+      </c>
+      <c r="G150" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A151" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D151" s="6">
+        <v>5.4379999999999997</v>
+      </c>
+      <c r="E151" s="6">
+        <v>3.3149999999999999</v>
+      </c>
+      <c r="F151" s="6">
+        <v>322</v>
+      </c>
+      <c r="G151" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A152" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D152" s="6">
+        <v>6.1589999999999998</v>
+      </c>
+      <c r="E152" s="6">
+        <v>3.6520000000000001</v>
+      </c>
+      <c r="F152" s="6">
+        <v>649</v>
+      </c>
+      <c r="G152" s="6">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
